--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N154_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N154_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.78266406197592</v>
+        <v>1.752182910071087</v>
       </c>
       <c r="D2" t="n">
-        <v>10.95704325907778</v>
+        <v>1.78051952960014</v>
       </c>
       <c r="E2" t="n">
-        <v>18.40155866367175</v>
+        <v>2.990253282846659</v>
       </c>
       <c r="F2" t="n">
-        <v>18.1198081040725</v>
+        <v>2.944468816911781</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.58578138931941</v>
+        <v>7.732689475764404</v>
       </c>
       <c r="D3" t="n">
-        <v>47.19665946722278</v>
+        <v>7.669457163423702</v>
       </c>
       <c r="E3" t="n">
-        <v>18.40155866367175</v>
+        <v>2.990253282846659</v>
       </c>
       <c r="F3" t="n">
-        <v>18.1198081040725</v>
+        <v>2.944468816911781</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
